--- a/Output/lapop_descriptive_means.xlsx
+++ b/Output/lapop_descriptive_means.xlsx
@@ -1,96 +1,86 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dec977f0560f05bf/BID/Papers Valerie/Ley de nietos/Argentina/Output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{0091A0DC-FF8E-C949-8FDD-A0303AEC2C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="22460" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Means by Spanish quintile" sheetId="1" r:id="rId1"/>
-    <sheet name="Means by migration intent" sheetId="2" r:id="rId2"/>
+    <sheet name="Means by Spanish quintile" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Means by migration intent" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
-  <si>
-    <t>Exposure</t>
-  </si>
-  <si>
-    <t>Share quintile</t>
-  </si>
-  <si>
-    <t>Observations</t>
-  </si>
-  <si>
-    <t>Left-right ideology</t>
-  </si>
-  <si>
-    <t>Previous vote</t>
-  </si>
-  <si>
-    <t>Party identification</t>
-  </si>
-  <si>
-    <t>Vote intention</t>
-  </si>
-  <si>
-    <t>Blank/null vote intention</t>
-  </si>
-  <si>
-    <t>Community meetings</t>
-  </si>
-  <si>
-    <t>Spanish share 1936-1955</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>Q3</t>
-  </si>
-  <si>
-    <t>Q4</t>
-  </si>
-  <si>
-    <t>Q5</t>
-  </si>
-  <si>
-    <t>Spanish share 1956-1978</t>
-  </si>
-  <si>
-    <t>Migration intent</t>
-  </si>
-  <si>
-    <t>Does not intend to migrate</t>
-  </si>
-  <si>
-    <t>Intends to migrate</t>
-  </si>
-  <si>
-    <t>No response</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t xml:space="preserve">Exposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share quintile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left-right ideology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous vote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party identification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vote intention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blank/null vote intention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community meetings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish share 1936-1955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish share 1956-1978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migration intent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does not intend to migrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intends to migrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No response</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -119,23 +109,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -417,11 +397,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,308 +430,308 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2">
-        <v>1216</v>
-      </c>
-      <c r="D2" s="1">
-        <v>5.7187176835573901</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.85737840065952198</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.25371900826446298</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.91595033428844297</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0.15849843587069901</v>
-      </c>
-      <c r="I2" s="1">
-        <v>9.5551894563426706E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C2" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.71871768355739</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.857378400659522</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.253719008264463</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.915950334288443</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.158498435870699</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0955518945634267</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
-        <v>1216</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D3" t="n">
         <v>5.54600606673407</v>
       </c>
-      <c r="E3" s="1">
-        <v>0.82392026578073096</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0.22165387894288099</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="E3" t="n">
+        <v>0.823920265780731</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.221653878942881</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.880077369439072</v>
       </c>
-      <c r="H3" s="1">
-        <v>0.18681318681318701</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="H3" t="n">
+        <v>0.186813186813187</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.102414654454621</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4">
-        <v>1216</v>
-      </c>
-      <c r="D4" s="1">
-        <v>5.5710059171597601</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.82906688687035501</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.26276150627615102</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.89748549323017401</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="C4" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.57100591715976</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.829066886870355</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.262761506276151</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.897485493230174</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.162715517241379</v>
       </c>
-      <c r="I4" s="1">
-        <v>9.4806265457543296E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I4" t="n">
+        <v>0.0948062654575433</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5">
-        <v>1216</v>
-      </c>
-      <c r="D5" s="1">
-        <v>5.1137667304015304</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.83223140495867798</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.22636815920398001</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.89003759398496196</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0.13093980992608201</v>
-      </c>
-      <c r="I5" s="1">
-        <v>9.6296296296296297E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C5" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.11376673040153</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.832231404958678</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.22636815920398</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.890037593984962</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.130939809926082</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0962962962962963</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6">
-        <v>1216</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C6" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D6" t="n">
         <v>5.23285024154589</v>
       </c>
-      <c r="E6" s="1">
-        <v>0.80329218106995903</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0.803292181069959</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.233139050791007</v>
       </c>
-      <c r="G6" s="1">
-        <v>0.88480154888673801</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="G6" t="n">
+        <v>0.884801548886738</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.12472647702407</v>
       </c>
-      <c r="I6" s="1">
-        <v>9.7861842105263205E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I6" t="n">
+        <v>0.0978618421052632</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
-        <v>1216</v>
-      </c>
-      <c r="D7" s="1">
-        <v>5.7135362014690498</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.84596375617792396</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0.26076158940397398</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.89569377990430599</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0.17521367521367501</v>
-      </c>
-      <c r="I7" s="1">
-        <v>9.2409240924092403E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C7" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.71353620146905</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.845963756177924</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.260761589403974</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.895693779904306</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.175213675213675</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0924092409240924</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8">
-        <v>1216</v>
-      </c>
-      <c r="D8" s="1">
-        <v>5.4904714142427302</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="C8" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.49047141424273</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.824938067712634</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" t="n">
         <v>0.236076475477972</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="n">
         <v>0.888363292336802</v>
       </c>
-      <c r="H8" s="1">
-        <v>0.16932907348242801</v>
-      </c>
-      <c r="I8" s="1">
-        <v>9.375E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H8" t="n">
+        <v>0.169329073482428</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.09375</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>15</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9">
-        <v>1216</v>
-      </c>
-      <c r="D9" s="1">
-        <v>5.6075322101090199</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.83471760797342198</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="C9" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.60753221010902</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.834717607973422</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.224315068493151</v>
       </c>
-      <c r="G9" s="1">
-        <v>0.89618021547502402</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0.16065573770491801</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="G9" t="n">
+        <v>0.896180215475024</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.160655737704918</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.1075</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10">
-        <v>1216</v>
-      </c>
-      <c r="D10" s="1">
-        <v>5.3313840155945398</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.82110469909315698</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.23192019950124701</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0.89645254074784297</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0.14866310160427801</v>
-      </c>
-      <c r="I10" s="1">
-        <v>8.8888888888888906E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C10" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.33138401559454</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.821104699093157</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.231920199501247</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.896452540747843</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.148663101604278</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0888888888888889</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11">
-        <v>1216</v>
-      </c>
-      <c r="D11" s="1">
-        <v>5.0487804878048799</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0.81915772089182504</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0.24438902743142099</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0.89196940726577401</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="C11" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.04878048780488</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.819157720891825</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.244389027431421</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.891969407265774</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.109324758842444</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" t="n">
         <v>0.104440789473684</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -777,86 +757,86 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>5135</v>
       </c>
-      <c r="C2" s="1">
-        <v>5.4502729646332799</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.84823000195579901</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.24589190259354601</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.89325068870523405</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="C2" t="n">
+        <v>5.45027296463328</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.848230001955799</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.245891902593546</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.893250688705234</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.143150860961193</v>
       </c>
-      <c r="H2" s="1">
-        <v>9.2259577795152495E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H2" t="n">
+        <v>0.0922595777951525</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>845</v>
       </c>
-      <c r="C3" s="1">
-        <v>5.2819499341238503</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.72123368920522002</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.20665083135391901</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="C3" t="n">
+        <v>5.28194993412385</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.721233689205219</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.206650831353919</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.897535667963684</v>
       </c>
-      <c r="G3" s="1">
-        <v>0.20664739884393099</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0.13151658767772501</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G3" t="n">
+        <v>0.206647398843931</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.131516587677725</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>100</v>
       </c>
-      <c r="C4" s="1">
-        <v>5.7974683544303804</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.76288659793814395</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.19565217391304299</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.88235294117647001</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="C4" t="n">
+        <v>5.79746835443038</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.762886597938144</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.195652173913043</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.882352941176471</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.146666666666667</v>
       </c>
-      <c r="H4" s="1">
-        <v>7.0707070707070704E-2</v>
+      <c r="H4" t="n">
+        <v>0.0707070707070707</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>